--- a/artfynd/A 8472-2020 artfynd.xlsx
+++ b/artfynd/A 8472-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8472-2020 artfynd.xlsx
+++ b/artfynd/A 8472-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3618,10 +3618,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>82396422</v>
+        <v>82396542</v>
       </c>
       <c r="B24" t="n">
-        <v>95511</v>
+        <v>93145</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3634,37 +3634,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221944</v>
+        <v>2667</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Neckera complanata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(Hedw.) Huebener</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Rasbo kyrka, 3,1 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>663801.9168326568</v>
+        <v>663830.0920974603</v>
       </c>
       <c r="R24" t="n">
-        <v>6648303.787582435</v>
+        <v>6648393.85131752</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3718,6 +3719,26 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3738,10 +3759,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>82396542</v>
+        <v>82397326</v>
       </c>
       <c r="B25" t="n">
-        <v>93145</v>
+        <v>78479</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3750,42 +3771,45 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>392</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,2 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>663830.0920974603</v>
+        <v>663831.1003173133</v>
       </c>
       <c r="R25" t="n">
-        <v>6648393.85131752</v>
+        <v>6648359.775384213</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3879,10 +3903,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>82397326</v>
+        <v>82397332</v>
       </c>
       <c r="B26" t="n">
-        <v>78479</v>
+        <v>78503</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3891,45 +3915,40 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>392</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rasbo kyrka. 3,2 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>663831.1003173133</v>
+        <v>663830.0476899946</v>
       </c>
       <c r="R26" t="n">
-        <v>6648359.775384213</v>
+        <v>6648394.852891956</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4023,10 +4042,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>82397332</v>
+        <v>82396549</v>
       </c>
       <c r="B27" t="n">
-        <v>78503</v>
+        <v>93132</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4039,25 +4058,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>2671</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4065,10 +4086,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>663830.0476899946</v>
+        <v>663806.1109389452</v>
       </c>
       <c r="R27" t="n">
-        <v>6648394.852891956</v>
+        <v>6648435.940230925</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4162,10 +4183,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>82396549</v>
+        <v>82397333</v>
       </c>
       <c r="B28" t="n">
-        <v>93132</v>
+        <v>78602</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4178,27 +4199,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2671</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4206,10 +4230,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>663806.1109389452</v>
+        <v>663794.8932203982</v>
       </c>
       <c r="R28" t="n">
-        <v>6648435.940230925</v>
+        <v>6648416.877570424</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4303,10 +4327,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>82397333</v>
+        <v>82397328</v>
       </c>
       <c r="B29" t="n">
-        <v>78602</v>
+        <v>78503</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4319,41 +4343,36 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,2 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>663794.8932203982</v>
+        <v>663835.7795583471</v>
       </c>
       <c r="R29" t="n">
-        <v>6648416.877570424</v>
+        <v>6648344.929530471</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4447,10 +4466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>82397328</v>
+        <v>82396537</v>
       </c>
       <c r="B30" t="n">
-        <v>78503</v>
+        <v>93145</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4463,25 +4482,27 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>2667</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Neckera complanata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) Huebener</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4489,10 +4510,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>663835.7795583471</v>
+        <v>663841.0483115042</v>
       </c>
       <c r="R30" t="n">
-        <v>6648344.929530471</v>
+        <v>6648384.8034296</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4562,9 +4583,12 @@
           <t>Bark på levande träd</t>
         </is>
       </c>
+      <c r="AN30" t="n">
+        <v>3</v>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>3 substratenheter # Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4586,10 +4610,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>82396537</v>
+        <v>82396552</v>
       </c>
       <c r="B31" t="n">
-        <v>93145</v>
+        <v>93132</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4602,21 +4626,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4626,14 +4650,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rasbo kyrka. 3,2 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>663841.0483115042</v>
+        <v>663816.8005475225</v>
       </c>
       <c r="R31" t="n">
-        <v>6648384.8034296</v>
+        <v>6648432.901774015</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4688,27 +4712,14 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AN31" t="n">
-        <v>3</v>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>3 substratenheter # Bark on living woody plant # Populus tremula</t>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4730,7 +4741,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>82396552</v>
+        <v>82396533</v>
       </c>
       <c r="B32" t="n">
         <v>93132</v>
@@ -4770,14 +4781,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,2 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>663816.8005475225</v>
+        <v>663841.9819122088</v>
       </c>
       <c r="R32" t="n">
-        <v>6648432.901774015</v>
+        <v>6648307.069179814</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4861,10 +4872,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>82396533</v>
+        <v>82396426</v>
       </c>
       <c r="B33" t="n">
-        <v>93132</v>
+        <v>98520</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4877,38 +4888,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2671</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rasbo kyrka. 3,2 km O-ut, Upl</t>
+          <t>Rasbo kyrka, 3,2 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>663841.9819122088</v>
+        <v>663848.8444233555</v>
       </c>
       <c r="R33" t="n">
-        <v>6648307.069179814</v>
+        <v>6648345.00705043</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4962,16 +4972,6 @@
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4992,7 +4992,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>82396426</v>
+        <v>82396424</v>
       </c>
       <c r="B34" t="n">
         <v>98520</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>663848.8444233555</v>
+        <v>663810.9464651697</v>
       </c>
       <c r="R34" t="n">
-        <v>6648345.00705043</v>
+        <v>6648304.187864395</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5112,10 +5112,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>82396424</v>
+        <v>82397337</v>
       </c>
       <c r="B35" t="n">
-        <v>98520</v>
+        <v>78503</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5128,37 +5128,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Rasbo kyrka, 3,2 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>663810.9464651697</v>
+        <v>663829.9489337627</v>
       </c>
       <c r="R35" t="n">
-        <v>6648304.187864395</v>
+        <v>6648465.095876666</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5212,6 +5212,26 @@
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Populus tremula</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -5232,10 +5252,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>82397337</v>
+        <v>82396536</v>
       </c>
       <c r="B36" t="n">
-        <v>78503</v>
+        <v>92939</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5248,37 +5268,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>2779</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,2 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>663829.9489337627</v>
+        <v>663856.1509157108</v>
       </c>
       <c r="R36" t="n">
-        <v>6648465.095876666</v>
+        <v>6648372.928765072</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5333,24 +5354,14 @@
       <c r="AG36" t="b">
         <v>0</v>
       </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Block (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Populus tremula</t>
+          <t>Rock (&gt; 200 mm)</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5372,10 +5383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>82396536</v>
+        <v>82396425</v>
       </c>
       <c r="B37" t="n">
-        <v>92939</v>
+        <v>98520</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5388,38 +5399,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rasbo kyrka. 3,2 km O-ut, Upl</t>
+          <t>Rasbo kyrka, 3,2 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>663856.1509157108</v>
+        <v>663854.7673348853</v>
       </c>
       <c r="R37" t="n">
-        <v>6648372.928765072</v>
+        <v>6648302.116476203</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5473,16 +5483,6 @@
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -5503,10 +5503,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>82396425</v>
+        <v>82396551</v>
       </c>
       <c r="B38" t="n">
-        <v>98520</v>
+        <v>93145</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5519,37 +5519,38 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neckera complanata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Huebener</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Rasbo kyrka, 3,2 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>663854.7673348853</v>
+        <v>663816.8005475225</v>
       </c>
       <c r="R38" t="n">
-        <v>6648302.116476203</v>
+        <v>6648432.901774015</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5603,6 +5604,16 @@
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5623,10 +5634,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>82396551</v>
+        <v>82397334</v>
       </c>
       <c r="B39" t="n">
-        <v>93145</v>
+        <v>78503</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5639,27 +5650,25 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2667</v>
+        <v>6456</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5667,10 +5676,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>663816.8005475225</v>
+        <v>663814.2306169576</v>
       </c>
       <c r="R39" t="n">
-        <v>6648432.901774015</v>
+        <v>6648400.172886807</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5725,14 +5734,24 @@
       <c r="AG39" t="b">
         <v>0</v>
       </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>Block (&gt; 200 mm)</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Rock (&gt; 200 mm)</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5754,10 +5773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>82397334</v>
+        <v>82396421</v>
       </c>
       <c r="B40" t="n">
-        <v>78503</v>
+        <v>98520</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5770,36 +5789,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
+          <t>Rasbo kyrka, 3,0 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>663814.2306169576</v>
+        <v>663715.1290842074</v>
       </c>
       <c r="R40" t="n">
-        <v>6648400.172886807</v>
+        <v>6648390.763001939</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5853,26 +5873,6 @@
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5893,10 +5893,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>82396421</v>
+        <v>82396544</v>
       </c>
       <c r="B41" t="n">
-        <v>98520</v>
+        <v>93145</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5909,37 +5909,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neckera complanata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Huebener</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Rasbo kyrka, 3,0 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>663715.1290842074</v>
+        <v>663782.8762756366</v>
       </c>
       <c r="R41" t="n">
-        <v>6648390.763001939</v>
+        <v>6648415.843128731</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5993,6 +5994,16 @@
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -6013,10 +6024,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>82396544</v>
+        <v>82397324</v>
       </c>
       <c r="B42" t="n">
-        <v>93145</v>
+        <v>78527</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6029,27 +6040,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2667</v>
+        <v>229497</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -6057,10 +6071,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>663782.8762756366</v>
+        <v>663851.1634737065</v>
       </c>
       <c r="R42" t="n">
-        <v>6648415.843128731</v>
+        <v>6648474.064752582</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6115,14 +6129,24 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Block (&gt; 200 mm)</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Rock (&gt; 200 mm)</t>
+          <t>Bark on living woody plant # Populus tremula</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6144,10 +6168,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>82397324</v>
+        <v>82397325</v>
       </c>
       <c r="B43" t="n">
-        <v>78527</v>
+        <v>78602</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6160,41 +6184,41 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,2 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>663851.1634737065</v>
+        <v>663831.1003173133</v>
       </c>
       <c r="R43" t="n">
-        <v>6648474.064752582</v>
+        <v>6648359.775384213</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6288,10 +6312,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>82397325</v>
+        <v>82397323</v>
       </c>
       <c r="B44" t="n">
-        <v>78602</v>
+        <v>78503</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6304,41 +6328,36 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6463</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Rasbo kyrka. 3,2 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>663831.1003173133</v>
+        <v>663851.1634737065</v>
       </c>
       <c r="R44" t="n">
-        <v>6648359.775384213</v>
+        <v>6648474.064752582</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6432,7 +6451,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>82397323</v>
+        <v>82397327</v>
       </c>
       <c r="B45" t="n">
         <v>78503</v>
@@ -6470,14 +6489,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,2 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>663851.1634737065</v>
+        <v>663832.014779022</v>
       </c>
       <c r="R45" t="n">
-        <v>6648474.064752582</v>
+        <v>6648361.823034054</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6571,7 +6590,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>82397327</v>
+        <v>82397329</v>
       </c>
       <c r="B46" t="n">
         <v>78503</v>
@@ -6613,10 +6632,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>663832.014779022</v>
+        <v>663856.1509157108</v>
       </c>
       <c r="R46" t="n">
-        <v>6648361.823034054</v>
+        <v>6648372.928765072</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6710,10 +6729,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>82397329</v>
+        <v>82396427</v>
       </c>
       <c r="B47" t="n">
-        <v>78503</v>
+        <v>98520</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6726,36 +6745,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>222498</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Rasbo kyrka. 3,2 km O-ut, Upl</t>
+          <t>Rasbo kyrka, 3,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>663856.1509157108</v>
+        <v>663806.8393221445</v>
       </c>
       <c r="R47" t="n">
-        <v>6648372.928765072</v>
+        <v>6648396.834587585</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6809,26 +6829,6 @@
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Populus tremula</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6849,10 +6849,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>82396427</v>
+        <v>82396538</v>
       </c>
       <c r="B48" t="n">
-        <v>98520</v>
+        <v>92939</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6865,37 +6865,38 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>222498</v>
+        <v>2779</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Rasbo kyrka, 3,1 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>663806.8393221445</v>
+        <v>663830.0476899946</v>
       </c>
       <c r="R48" t="n">
-        <v>6648396.834587585</v>
+        <v>6648394.852891956</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6949,6 +6950,16 @@
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Block (&gt; 200 mm)</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Rock (&gt; 200 mm)</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6969,10 +6980,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>82396538</v>
+        <v>82396429</v>
       </c>
       <c r="B49" t="n">
-        <v>92939</v>
+        <v>98520</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6985,38 +6996,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2779</v>
+        <v>222498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
+          <t>Rasbo kyrka, 3,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>663830.0476899946</v>
+        <v>663822.983757</v>
       </c>
       <c r="R49" t="n">
-        <v>6648394.852891956</v>
+        <v>6648474.822284339</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7070,16 +7080,6 @@
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Block (&gt; 200 mm)</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Rock (&gt; 200 mm)</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -7100,10 +7100,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>82396429</v>
+        <v>82396541</v>
       </c>
       <c r="B50" t="n">
-        <v>98520</v>
+        <v>93145</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7116,37 +7116,38 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neckera complanata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Huebener</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Rasbo kyrka, 3,1 km O-ut, Upl</t>
+          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>663822.983757</v>
+        <v>663816.7609848998</v>
       </c>
       <c r="R50" t="n">
-        <v>6648474.822284339</v>
+        <v>6648399.783296932</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7201,6 +7202,16 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Sitter på litet lövträd.</t>
+        </is>
+      </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
@@ -7213,137 +7224,6 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>82396541</v>
-      </c>
-      <c r="B51" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>2667</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Platt fjädermossa</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Neckera complanata</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Hedw.) Huebener</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Rasbo kyrka. 3,1 km O-ut, Upl</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>663816.7609848998</v>
-      </c>
-      <c r="R51" t="n">
-        <v>6648399.783296932</v>
-      </c>
-      <c r="S51" t="n">
-        <v>10</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Rasbo</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2020-02-23</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2020-02-23</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Sitter på litet lövträd.</t>
-        </is>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
